--- a/data/trans_orig/P19C05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C05-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164945</t>
+          <t>164265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>210983</t>
+          <t>211343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>256011</t>
+          <t>256618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>314394</t>
+          <t>314125</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>439366</t>
+          <t>435867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>512559</t>
+          <t>508540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478382</t>
+          <t>478022</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>524420</t>
+          <t>525100</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>644565</t>
+          <t>644834</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>702948</t>
+          <t>702341</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1135765</t>
+          <t>1139784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1208958</t>
+          <t>1212457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80339</t>
+          <t>80424</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>120952</t>
+          <t>119789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94003</t>
+          <t>96770</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>137484</t>
+          <t>138881</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>186235</t>
+          <t>188206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>244240</t>
+          <t>245696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1193496</t>
+          <t>1194659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1234109</t>
+          <t>1234024</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1235711</t>
+          <t>1234314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1279192</t>
+          <t>1276425</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2443403</t>
+          <t>2441947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2501408</t>
+          <t>2499437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36275</t>
+          <t>37091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63862</t>
+          <t>64079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28559</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51943</t>
+          <t>52656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70458</t>
+          <t>70680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106397</t>
+          <t>108108</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387067</t>
+          <t>386850</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>414654</t>
+          <t>413838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>356840</t>
+          <t>356127</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>380224</t>
+          <t>380334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>753315</t>
+          <t>751604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>789254</t>
+          <t>789032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>301710</t>
+          <t>303299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>365333</t>
+          <t>369199</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>404636</t>
+          <t>406123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>484194</t>
+          <t>483010</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>729461</t>
+          <t>726894</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>831117</t>
+          <t>827500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2089409</t>
+          <t>2085543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2153032</t>
+          <t>2151443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2256743</t>
+          <t>2257927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2336301</t>
+          <t>2334814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4364562</t>
+          <t>4368179</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4466218</t>
+          <t>4468785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2012 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>190452</t>
+          <t>191049</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>242291</t>
+          <t>244100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>342391</t>
+          <t>343652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>407210</t>
+          <t>409415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>552168</t>
+          <t>552764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>637722</t>
+          <t>639250</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>536883</t>
+          <t>535074</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>588722</t>
+          <t>588125</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>721032</t>
+          <t>718827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>785851</t>
+          <t>784590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1269693</t>
+          <t>1268165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1355247</t>
+          <t>1354651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>152585</t>
+          <t>153179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>208741</t>
+          <t>209815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>141119</t>
+          <t>138529</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>189673</t>
+          <t>192729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>310110</t>
+          <t>309177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>380919</t>
+          <t>382364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1479537</t>
+          <t>1478463</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1535693</t>
+          <t>1535099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1400605</t>
+          <t>1397549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1449159</t>
+          <t>1451749</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2897636</t>
+          <t>2896191</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2968445</t>
+          <t>2969378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>28197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53409</t>
+          <t>54817</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45047</t>
+          <t>46979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>54879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89942</t>
+          <t>90142</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>388725</t>
+          <t>387317</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>415765</t>
+          <t>413937</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>378676</t>
+          <t>376744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>402040</t>
+          <t>401225</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>775915</t>
+          <t>775715</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>810384</t>
+          <t>810978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>395029</t>
+          <t>397286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>476711</t>
+          <t>478207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>527466</t>
+          <t>527717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>614199</t>
+          <t>615638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>947588</t>
+          <t>946072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1070673</t>
+          <t>1073643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2432875</t>
+          <t>2431379</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2514557</t>
+          <t>2512300</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2528044</t>
+          <t>2526605</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2614777</t>
+          <t>2614526</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4981155</t>
+          <t>4978185</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5104240</t>
+          <t>5105756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79493</t>
+          <t>79158</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114617</t>
+          <t>112546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115069</t>
+          <t>115987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158134</t>
+          <t>161226</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206607</t>
+          <t>205764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>259607</t>
+          <t>257585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>342802</t>
+          <t>344873</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>377926</t>
+          <t>378261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>480740</t>
+          <t>477648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>523805</t>
+          <t>522887</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>836686</t>
+          <t>838708</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>889686</t>
+          <t>890529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124511</t>
+          <t>126203</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>171956</t>
+          <t>176513</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135002</t>
+          <t>134255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187248</t>
+          <t>182943</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>274339</t>
+          <t>273097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>342004</t>
+          <t>342782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1524649</t>
+          <t>1520092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1572094</t>
+          <t>1570402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1521471</t>
+          <t>1525776</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1573717</t>
+          <t>1574464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3063320</t>
+          <t>3062542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3130985</t>
+          <t>3132227</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27713</t>
+          <t>27675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>52184</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25141</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49995</t>
+          <t>50861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58418</t>
+          <t>59085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94768</t>
+          <t>93138</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>447023</t>
+          <t>447060</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471531</t>
+          <t>471569</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>458325</t>
+          <t>457459</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>483179</t>
+          <t>482035</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>912796</t>
+          <t>914426</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>949146</t>
+          <t>948479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>253895</t>
+          <t>249293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>316582</t>
+          <t>316620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>300560</t>
+          <t>294814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>370441</t>
+          <t>366904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>569396</t>
+          <t>571697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>667737</t>
+          <t>660194</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2336687</t>
+          <t>2336649</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2399374</t>
+          <t>2403976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2485472</t>
+          <t>2489009</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2555353</t>
+          <t>2561099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4841445</t>
+          <t>4848988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4939786</t>
+          <t>4937485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74977</t>
+          <t>73700</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103488</t>
+          <t>103162</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>174932</t>
+          <t>174688</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>210128</t>
+          <t>208354</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>258847</t>
+          <t>259499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303967</t>
+          <t>305983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>380953</t>
+          <t>381279</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>409464</t>
+          <t>410741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>511488</t>
+          <t>513262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>546684</t>
+          <t>546928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>902090</t>
+          <t>900074</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>947210</t>
+          <t>946558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122633</t>
+          <t>125185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>212657</t>
+          <t>214412</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110294</t>
+          <t>117176</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184438</t>
+          <t>185678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>266655</t>
+          <t>266503</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>383722</t>
+          <t>381115</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2017880</t>
+          <t>2016125</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2107904</t>
+          <t>2105352</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2013468</t>
+          <t>2012228</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2087612</t>
+          <t>2080730</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4044720</t>
+          <t>4047327</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4161787</t>
+          <t>4161939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41555</t>
+          <t>41217</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68705</t>
+          <t>67485</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34989</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58136</t>
+          <t>58375</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84377</t>
+          <t>82926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118313</t>
+          <t>116922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>562611</t>
+          <t>563831</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>589761</t>
+          <t>590099</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>593475</t>
+          <t>593236</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>616622</t>
+          <t>615503</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1164614</t>
+          <t>1166005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1198550</t>
+          <t>1200001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>244908</t>
+          <t>245278</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>359581</t>
+          <t>358702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>323327</t>
+          <t>321164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>438024</t>
+          <t>435450</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>614301</t>
+          <t>629800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>779422</t>
+          <t>776165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2986712</t>
+          <t>2987591</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3101385</t>
+          <t>3101015</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3133109</t>
+          <t>3135683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3247806</t>
+          <t>3249969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,17 +6749,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6201322</t>
+          <t>6201323</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6138004</t>
+          <t>6141262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6303125</t>
+          <t>6287627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6917426</t>
+          <t>6917427</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6917426</t>
+          <t>6917427</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6917426</t>
+          <t>6917427</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P19C05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C05-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164265</t>
+          <t>164302</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>211343</t>
+          <t>209305</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>256618</t>
+          <t>260185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>314125</t>
+          <t>315471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>435867</t>
+          <t>440322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>508540</t>
+          <t>511929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478022</t>
+          <t>480060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>525100</t>
+          <t>525063</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>644834</t>
+          <t>643488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>702341</t>
+          <t>698774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1139784</t>
+          <t>1136395</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1212457</t>
+          <t>1208002</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80424</t>
+          <t>80389</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119789</t>
+          <t>119417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96770</t>
+          <t>95706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138881</t>
+          <t>136416</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>188206</t>
+          <t>185297</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245696</t>
+          <t>243997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1194659</t>
+          <t>1195031</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1234024</t>
+          <t>1234059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1234314</t>
+          <t>1236779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1276425</t>
+          <t>1277489</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2441947</t>
+          <t>2443646</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2499437</t>
+          <t>2502346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37091</t>
+          <t>36609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64079</t>
+          <t>63366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>28370</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52656</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70680</t>
+          <t>70103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108108</t>
+          <t>106502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>386850</t>
+          <t>387563</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>413838</t>
+          <t>414320</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>356127</t>
+          <t>356555</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>380334</t>
+          <t>380413</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>751604</t>
+          <t>753210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>789032</t>
+          <t>789609</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>303299</t>
+          <t>299928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>369199</t>
+          <t>369344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>406123</t>
+          <t>403825</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>483010</t>
+          <t>477766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>726894</t>
+          <t>722756</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>827500</t>
+          <t>825630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2085543</t>
+          <t>2085398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2151443</t>
+          <t>2154814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2257927</t>
+          <t>2263171</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2334814</t>
+          <t>2337112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4368179</t>
+          <t>4370049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4468785</t>
+          <t>4472923</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>191049</t>
+          <t>191504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>244100</t>
+          <t>243434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>343652</t>
+          <t>343405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>409415</t>
+          <t>408778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>552764</t>
+          <t>549765</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>639250</t>
+          <t>634091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>535074</t>
+          <t>535740</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>588125</t>
+          <t>587670</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>718827</t>
+          <t>719464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>784590</t>
+          <t>784837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1268165</t>
+          <t>1273324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1354651</t>
+          <t>1357650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,18%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>153179</t>
+          <t>151510</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>209815</t>
+          <t>205886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138529</t>
+          <t>141140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>192729</t>
+          <t>192405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>309177</t>
+          <t>311970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>382364</t>
+          <t>379553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1478463</t>
+          <t>1482392</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1535099</t>
+          <t>1536768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1397549</t>
+          <t>1397873</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1451749</t>
+          <t>1449138</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2896191</t>
+          <t>2899002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2969378</t>
+          <t>2966585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28197</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54817</t>
+          <t>55736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22498</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46979</t>
+          <t>45034</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54879</t>
+          <t>56137</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90142</t>
+          <t>92574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387317</t>
+          <t>386398</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>413937</t>
+          <t>414590</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>376744</t>
+          <t>378689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>401225</t>
+          <t>400786</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>775715</t>
+          <t>773283</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>810978</t>
+          <t>809720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>397286</t>
+          <t>395061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>478207</t>
+          <t>472351</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>527717</t>
+          <t>528982</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>615638</t>
+          <t>617833</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>946072</t>
+          <t>952290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1073643</t>
+          <t>1072190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2431379</t>
+          <t>2437235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2512300</t>
+          <t>2514525</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2526605</t>
+          <t>2524410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2614526</t>
+          <t>2613261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4978185</t>
+          <t>4979638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5105756</t>
+          <t>5099538</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79158</t>
+          <t>80236</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112546</t>
+          <t>114814</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115987</t>
+          <t>115346</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>161226</t>
+          <t>158361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205764</t>
+          <t>204054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>257585</t>
+          <t>259857</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>344873</t>
+          <t>342605</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>378261</t>
+          <t>377183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>477648</t>
+          <t>480513</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>522887</t>
+          <t>523528</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>838708</t>
+          <t>836436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>890529</t>
+          <t>892239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,39%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126203</t>
+          <t>125997</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>176513</t>
+          <t>172700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134255</t>
+          <t>137544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182943</t>
+          <t>188440</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>273097</t>
+          <t>273991</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>342782</t>
+          <t>342087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1520092</t>
+          <t>1523905</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1570402</t>
+          <t>1570608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1525776</t>
+          <t>1520279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1574464</t>
+          <t>1571175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3062542</t>
+          <t>3063237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3132227</t>
+          <t>3131333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27675</t>
+          <t>27865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52184</t>
+          <t>52425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26285</t>
+          <t>25397</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50861</t>
+          <t>50764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59085</t>
+          <t>58413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93138</t>
+          <t>92892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>447060</t>
+          <t>446819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471569</t>
+          <t>471379</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>457459</t>
+          <t>457556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>482035</t>
+          <t>482923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>914426</t>
+          <t>914672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>948479</t>
+          <t>949151</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>249293</t>
+          <t>249353</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>316620</t>
+          <t>315889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>294814</t>
+          <t>299287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>366904</t>
+          <t>371840</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>571697</t>
+          <t>565874</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>660194</t>
+          <t>667983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2336649</t>
+          <t>2337380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2403976</t>
+          <t>2403916</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2489009</t>
+          <t>2484073</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2561099</t>
+          <t>2556626</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4848988</t>
+          <t>4841199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4937485</t>
+          <t>4943308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>88146</t>
+          <t>94715</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73700</t>
+          <t>80415</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103162</t>
+          <t>110409</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>192740</t>
+          <t>207437</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>174688</t>
+          <t>188378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>208354</t>
+          <t>224475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>280886</t>
+          <t>302151</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>259499</t>
+          <t>278983</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>305983</t>
+          <t>326726</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>396295</t>
+          <t>442564</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>381279</t>
+          <t>426870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410741</t>
+          <t>456864</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>528876</t>
+          <t>577155</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>513262</t>
+          <t>560117</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>546928</t>
+          <t>596214</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>925171</t>
+          <t>1019720</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>900074</t>
+          <t>995145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>946558</t>
+          <t>1042888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,89%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>178123</t>
+          <t>198635</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125185</t>
+          <t>173714</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>214412</t>
+          <t>227733</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>157193</t>
+          <t>177991</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>117176</t>
+          <t>157238</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>185678</t>
+          <t>199685</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>335315</t>
+          <t>376626</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>266503</t>
+          <t>346027</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>381115</t>
+          <t>413145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2052414</t>
+          <t>1947843</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2016125</t>
+          <t>1918745</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2105352</t>
+          <t>1972764</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2040713</t>
+          <t>1932601</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2012228</t>
+          <t>1910907</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2080730</t>
+          <t>1953354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4093127</t>
+          <t>3880444</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4047327</t>
+          <t>3843925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4161939</t>
+          <t>3911043</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,22 +6223,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>53726</t>
+          <t>58322</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41217</t>
+          <t>45857</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67485</t>
+          <t>73106</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46177</t>
+          <t>50052</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36108</t>
+          <t>39281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58375</t>
+          <t>62822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>99903</t>
+          <t>108373</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82926</t>
+          <t>91979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116922</t>
+          <t>128897</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -6336,27 +6336,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>577590</t>
+          <t>643519</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>563831</t>
+          <t>628735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>590099</t>
+          <t>655984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>605434</t>
+          <t>674361</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>593236</t>
+          <t>661591</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>615503</t>
+          <t>685132</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1183024</t>
+          <t>1317881</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1166005</t>
+          <t>1297357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1200001</t>
+          <t>1334275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>319995</t>
+          <t>351671</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>245278</t>
+          <t>316972</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>358702</t>
+          <t>387497</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>396109</t>
+          <t>435479</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>321164</t>
+          <t>404999</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>435450</t>
+          <t>469508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>716104</t>
+          <t>787150</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>629800</t>
+          <t>743519</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>776165</t>
+          <t>832958</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3026298</t>
+          <t>3033927</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2987591</t>
+          <t>2998101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3101015</t>
+          <t>3068626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3175024</t>
+          <t>3184118</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3135683</t>
+          <t>3150089</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3249969</t>
+          <t>3214598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6201323</t>
+          <t>6218045</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6141262</t>
+          <t>6172237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6287627</t>
+          <t>6261676</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3346293</t>
+          <t>3385598</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3346293</t>
+          <t>3385598</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3346293</t>
+          <t>3385598</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6917427</t>
+          <t>7005195</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6917427</t>
+          <t>7005195</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6917427</t>
+          <t>7005195</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
